--- a/Assmnt1_car_rental/Car Master List.csv.xlsx
+++ b/Assmnt1_car_rental/Car Master List.csv.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTMAR\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTMAR\OneDrive\Documents\GitHub\MS008\Assmnt1_car_rental\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E27BA37-DCBC-490D-AABE-76AA126A7670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{182F8B92-E78C-4851-9FFC-83CB0A48D3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{57EE94B0-8041-480F-A363-D29AF824B137}"/>
   </bookViews>
@@ -86,9 +86,6 @@
     <t>Y</t>
   </si>
   <si>
-    <t>31/07/2025</t>
-  </si>
-  <si>
     <t>Suzuki</t>
   </si>
   <si>
@@ -198,6 +195,9 @@
   </si>
   <si>
     <t>15/09/2025</t>
+  </si>
+  <si>
+    <t>15/08/2025</t>
   </si>
 </sst>
 </file>
@@ -641,10 +641,10 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
@@ -662,10 +662,10 @@
         <v>15</v>
       </c>
       <c r="J5" s="2">
-        <v>45901</v>
+        <v>45785</v>
       </c>
       <c r="K5" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -676,16 +676,16 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
         <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -697,16 +697,16 @@
         <v>1500</v>
       </c>
       <c r="I6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s">
         <v>21</v>
       </c>
-      <c r="J6" t="s">
-        <v>22</v>
-      </c>
       <c r="K6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -714,16 +714,16 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F7">
         <v>7</v>
@@ -741,10 +741,10 @@
         <v>45786</v>
       </c>
       <c r="K7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -752,16 +752,16 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
         <v>30</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>31</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>33</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -773,16 +773,16 @@
         <v>2500</v>
       </c>
       <c r="I8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" t="s">
         <v>21</v>
       </c>
-      <c r="J8" t="s">
-        <v>22</v>
-      </c>
       <c r="K8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -790,13 +790,13 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
         <v>34</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>36</v>
       </c>
       <c r="E9" t="s">
         <v>14</v>
@@ -817,7 +817,7 @@
         <v>45908</v>
       </c>
       <c r="K9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L9" t="s">
         <v>15</v>
@@ -831,13 +831,13 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
         <v>38</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>39</v>
-      </c>
-      <c r="E10" t="s">
-        <v>40</v>
       </c>
       <c r="F10">
         <v>7</v>
@@ -852,13 +852,13 @@
         <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -866,16 +866,16 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
         <v>41</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>42</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>43</v>
-      </c>
-      <c r="E11" t="s">
-        <v>44</v>
       </c>
       <c r="F11">
         <v>4</v>
@@ -893,7 +893,7 @@
         <v>45784</v>
       </c>
       <c r="K11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L11" t="s">
         <v>15</v>
@@ -907,10 +907,10 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
         <v>46</v>
-      </c>
-      <c r="D12" t="s">
-        <v>47</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
@@ -925,16 +925,16 @@
         <v>1500</v>
       </c>
       <c r="I12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" t="s">
         <v>21</v>
       </c>
-      <c r="J12" t="s">
-        <v>22</v>
-      </c>
       <c r="K12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -942,16 +942,16 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
         <v>48</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>49</v>
       </c>
-      <c r="D13" t="s">
-        <v>50</v>
-      </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -963,16 +963,16 @@
         <v>1800</v>
       </c>
       <c r="I13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" t="s">
         <v>21</v>
       </c>
-      <c r="J13" t="s">
-        <v>22</v>
-      </c>
       <c r="K13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -980,16 +980,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
         <v>51</v>
       </c>
-      <c r="D14" t="s">
-        <v>52</v>
-      </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F14">
         <v>7</v>
@@ -1007,10 +1007,10 @@
         <v>45817</v>
       </c>
       <c r="K14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
